--- a/tools/excel/anssi/ii-901/ii-901.xlsx
+++ b/tools/excel/anssi/ii-901/ii-901.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\anssi\ii-901\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D0482B-2E4C-46FC-83F0-CADE6FCDEF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9655FC11-664E-41B5-AD0B-62F37DC29446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="909">
   <si>
     <t>type</t>
   </si>
@@ -3914,9 +3914,7 @@
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="A27" s="7"/>
       <c r="B27" s="4">
         <v>3</v>
       </c>
